--- a/Template Import/Templates commission Draft.xlsx
+++ b/Template Import/Templates commission Draft.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B509430-ABBB-471E-8918-D87EA10AF28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CF7D77-901B-4AE8-ADB7-80ACBAE4D7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
   </bookViews>
   <sheets>
     <sheet name="h" sheetId="1" r:id="rId1"/>
     <sheet name="l" sheetId="2" r:id="rId2"/>
+    <sheet name="VENDOR+PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="271">
   <si>
     <t>DocNum</t>
   </si>
@@ -474,13 +475,721 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂຊກໄຊ ພລັສ ອີ-ຄອມເມີດ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-OAP-0002</t>
+  </si>
+  <si>
+    <t>ຂາຍຜ່ານແອັບອອນລາຍ</t>
+  </si>
+  <si>
+    <t>V-VT-OAP-0001</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນຈຸລະພາກທີ່ບໍ່ຮັບເງິນຝາກມັນນີ.ລາ ຈຳກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0004</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນ ອາລຸນໄຫມ່</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0002</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນ ໂຊກໄຊ</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0001</t>
+  </si>
+  <si>
+    <t>ນຸ້ຍ ສີປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0046</t>
+  </si>
+  <si>
+    <t>ພາວະລິນ ສີສະຫວັດ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0016</t>
+  </si>
+  <si>
+    <t>ພົງພາວັນ ມໍໄລພອນ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0013</t>
+  </si>
+  <si>
+    <t>ຂາຍຕົງຜູ້ຂາຍຂາຍເອງ ແລະ ມີການແນະນຳ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ລາວໂຕໂຢຕ້າ ບໍລິການ ຈຳກັດ (ສາຂາ ສີໂຄດ)</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0009</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ລາວໂຕໂຢຕ້າ ບໍລິການ ຈຳກັດ (ສາຂາ ທົ່ງຂັນຄຳ)</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0007</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ເອັມພາຍ ມໍເຕີ ລາວ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0006</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂອໂຕ ລາວ ຈຳກັຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0003</t>
+  </si>
+  <si>
+    <t>ຮ້ານ ຄຳທະວີ ປະດັບຍົນ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0001</t>
+  </si>
+  <si>
+    <t>ລູກຄ້າເຂົ້າມາຊື້ຕົງ</t>
+  </si>
+  <si>
+    <t>V-VT-D-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ໃຈອາລີ ອິນທະວົງ (ທະນາຄານ ລາວ-ຝຣັ່ງ)</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0005</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ເອຊີລິດາ QH</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0004</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ສົ່ງເສີມ ກະສິກຳ HQ</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0002</t>
+  </si>
+  <si>
+    <t>Maruhun HQ</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ພີເອັສຊີ ນາຍໜ້າປະກັນໄພ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0007</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ສາຍຝົນ ໂບຼກເກີ</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0004</t>
+  </si>
+  <si>
+    <t>KX BROKER</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0002</t>
+  </si>
+  <si>
+    <t>OAC BROKER</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ນ້ອຍ ສິລິມົງຄຸນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0075</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພູມິນ ໄກສອນເພັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0074</t>
+  </si>
+  <si>
+    <t>ນາງ ສຸດາພອນ ໂງ່ນກະເສີມສຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0072</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນມາລີ ຄັນທະວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0071</t>
+  </si>
+  <si>
+    <t>ນາງ ສິນໃຈ ໄຊຍະລາດ (ບໍລິສັດ ສຸກໃຈ ບໍລິການ ຈັດຫາງານ ຈໍາກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0069</t>
+  </si>
+  <si>
+    <t>ນາງ ວາດສະໜາ ວໍລະວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0068</t>
+  </si>
+  <si>
+    <t>ທ້າວ ເພັດສະພອນ ບຸນຍະນິດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0067</t>
+  </si>
+  <si>
+    <t>ນາງ ເພັດມະນີ ວໍລະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0065</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ຊີທີໄອ ໂລຈິດສະຕິກ (ລາວ) ຈຳກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0063</t>
+  </si>
+  <si>
+    <t>ນາງ ເກດສະໜາ ແສງທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0060</t>
+  </si>
+  <si>
+    <t>ນາງ ພູລິນິດ ອິນສີຊຽງໃໝ່</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0059</t>
+  </si>
+  <si>
+    <t>ນາງ ຂັນຄຳ ພົມມະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0058</t>
+  </si>
+  <si>
+    <t>ນາງ ນ້ອຍນາລີ ກຽດຕາວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0057</t>
+  </si>
+  <si>
+    <t>ນາງ ວິດາພອນ ໄພສານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0056</t>
+  </si>
+  <si>
+    <t>ທ້າວ ທອງວັນ ຄຳວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0055</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພອນໄຊ ຈັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0054</t>
+  </si>
+  <si>
+    <t>ນາງ ຈຸລະພອນ ເພັງສະຫວັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0053</t>
+  </si>
+  <si>
+    <t>ທ້າວ ວິພາກອນ ໂພທິສານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0051</t>
+  </si>
+  <si>
+    <t>ນາງ ພຸດທະສະຫວັນ ສັງໄຊຍະລາດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0050</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສົມອົກ ວິຣະສັກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0049</t>
+  </si>
+  <si>
+    <t>ນາງ ວິໄລລັກ ຄຳວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0048</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສອນປະເສີດ ພູມມາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0046</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ 14 ມີໄຊການຄ້າຂາອອກ-ຂາເຂົ້າ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0042</t>
+  </si>
+  <si>
+    <t>ນາງ ທອງໃສ ສິດຊະນະ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0040</t>
+  </si>
+  <si>
+    <t>ນາງ ນຸດດາວັນ ນວນສະຫວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0036</t>
+  </si>
+  <si>
+    <t>ທ້າວ ອິນທະຕອງ ແກ້ວສີລາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0035</t>
+  </si>
+  <si>
+    <t>ນາງ ລີຕ້າ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0034</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພານິດໄຊ ສີບຸນຍາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0028</t>
+  </si>
+  <si>
+    <t>ນາງ ສຸວັນທອນ ໄຊຍະລາດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0025</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນທະລົມ ລັດຖະມອນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0023</t>
+  </si>
+  <si>
+    <t>ນາງ ຈ່ອນນີ້ ກຸລາວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0021</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂຊກໄຊຈະເລີນຂົນສົ່ງ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0020</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຈັນສະໝອນ ໄຊຍະກຸມມານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0018</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳຈັນ ຊາມູນຕີຮ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0017</t>
+  </si>
+  <si>
+    <t>ນາງ ຈຳປາເພັດ ສຸທຳມະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0016</t>
+  </si>
+  <si>
+    <t>ທ້າວ ທອງພູນ ຂຸນບັນດິດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0015</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳຜັນ ຈັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0014</t>
+  </si>
+  <si>
+    <t>ນາງ ອຳພາພອນ ແຕ້ອຳພອນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0012</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພູມະສອນ ຮ່ວງຫວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0011</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳສີ ສີລິມຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0010</t>
+  </si>
+  <si>
+    <t>ນາງ ບົວລະພັນ ພົມສຸວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0009</t>
+  </si>
+  <si>
+    <t>ນາງ ອໍລະວີ ວິໄລວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0006</t>
+  </si>
+  <si>
+    <t>ນາງ ອຸດທະວີວອນ ບຸນທະຄຳ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0005</t>
+  </si>
+  <si>
+    <t>ທ້າວ ກິດຕິສັກ ນັນທະນາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0004</t>
+  </si>
+  <si>
+    <t>ທ້າວ ດວງພະຈັນ ສິງທອງມົນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003-06</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສີອຳພອນ ແສງສຸລິນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003-02</t>
+  </si>
+  <si>
+    <t>ນາງ ບຸນຮຽງ ຈັນທະສຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003</t>
+  </si>
+  <si>
+    <t>ນາງ ທິບພາພອນ ພົມມະຈັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0002</t>
+  </si>
+  <si>
+    <t>ທ້າວ ກຸ້ງ ສີນວນຈັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0001</t>
+  </si>
+  <si>
+    <t>ຄຳພູນ ສີດາວົງ</t>
+  </si>
+  <si>
+    <t>V-ST-ITF-0001</t>
+  </si>
+  <si>
+    <t>LAO TOYOTA SOUTHERN</t>
+  </si>
+  <si>
+    <t>V-ST-DL-0001</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ມາຣູຮານ ສາຂາ ຈຳປາສັກ</t>
+  </si>
+  <si>
+    <t>V-ST-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ນາຍໜ້າປະກັນໄພ ອາລາດິນ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-ST-BK-0001</t>
+  </si>
+  <si>
+    <t>ທ້າວ ເພັດສະໝອນ ສີລາເພັດ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0012</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄູນສະຫວັດ ວັນທອງ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0011</t>
+  </si>
+  <si>
+    <t>ນາງ ເກດມະນີ ຄູນວິໄຊ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0009</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສົມພິດ ພົມມະຈັກ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0008</t>
+  </si>
+  <si>
+    <t>ທ້າວ ບຸຸດສະດີ ສີພັນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0007</t>
+  </si>
+  <si>
+    <t>ນາງ ມະນີີວັນ ໄຊອາສາ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0005</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ເອັດສແອລ ທ່ອງທ່ຽວ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0004</t>
+  </si>
+  <si>
+    <t>ນາງ ສີອໍາພອນ ແກ້ວໂກມິນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0003</t>
+  </si>
+  <si>
+    <t>ນາງ ດາວພະໄທ ໄຊຍະສອນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0001</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>V-PMT-0001</t>
+  </si>
+  <si>
+    <t>ທ້າວ ໄຊ ວື</t>
+  </si>
+  <si>
+    <t>V-NT-ITF-0001</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ມາຣູຮານ ສາຂາ ຫຼວງພະບາງ</t>
+  </si>
+  <si>
+    <t>V-NT-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໄຊຍະສິດ ໂບຣກເກີ້ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-NT-BK-0001-02</t>
+  </si>
+  <si>
+    <t>V-NT-BK-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ລາທິນ ສີສົມສັກ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0015</t>
+  </si>
+  <si>
+    <t>ນາງ ແກ້ວອາມິດ ມີໄຊຄຳ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0013</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສີທະນົນ ພົມແສງປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0011</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0006</t>
+  </si>
+  <si>
+    <t>ທ້າວ ດອນແກ້ວ ວົງນາທີ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0002</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອື່ນໆ</t>
+  </si>
+  <si>
+    <t>624.13.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ອຳພອນ ພັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0001</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>624.12.00</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0020</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>624.11.00</t>
+  </si>
+  <si>
+    <t>ນາງ ພອນມະນີ ຂຸນທຳ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0016</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອຸດສາຫະກຳ</t>
+  </si>
+  <si>
+    <t>624.10.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສຸລິຍາ ພົມຂັນໄຊ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0014</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>624.09.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄິດສະໜາ ອຸ່ນແກ້ວມະນິວົງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0011</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>624.08.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈິນຕະນາ ນໍລະສິງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0010</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສູຂະພາບ</t>
+  </si>
+  <si>
+    <t>624.07.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ບຸນທະນອງ ຄຸນພະຈັນ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0007</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອຸບັດຕິເຫດສ່ວນບູກຄົນ</t>
+  </si>
+  <si>
+    <t>624.06.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນນະພາ ພອນມະນີ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0006</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>624.05.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄາລາເຕ້ ເທບພະວົງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0005</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>624.04.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ວົງສຸລິວັນ ວັນນະໄລ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0004</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກສະຫມັກໃຈ</t>
+  </si>
+  <si>
+    <t>624.03.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳແສງ ໄຊປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0002</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>624.02.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນສຸດາ ຈັນທະດວງສີ</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,6 +1242,12 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -597,7 +1312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -618,6 +1333,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,23 +1669,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72421B36-76D0-40A6-BFD5-6431BAAA1FA9}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="6"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1039,7 +1755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1080,22 +1796,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617443EE-1F70-4C65-9F9D-8265A5A09A24}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.796875" style="6"/>
+    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1875,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1193,4 +1909,1466 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56115C20-D91B-46DD-B77B-B0C3859B037D}">
+  <dimension ref="A1:G108"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="30.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="F1" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" s="16"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="16"/>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="16"/>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" s="16"/>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F41" s="16"/>
+      <c r="G41" s="12"/>
+    </row>
+    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" s="16"/>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="F43" s="16"/>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F44" s="16"/>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="16"/>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="16"/>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47" s="16"/>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" s="16"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F49" s="16"/>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="16"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F51" s="16"/>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F52" s="16"/>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" s="16"/>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F54" s="16"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" s="16"/>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F56" s="16"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" s="16"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F58" s="16"/>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F59" s="16"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F60" s="16"/>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="16"/>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F62" s="16"/>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F63" s="16"/>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F64" s="16"/>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F65" s="16"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" s="16"/>
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F67" s="16"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F68" s="16"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F69" s="16"/>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F70" s="16"/>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F71" s="16"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="16"/>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F73" s="16"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F74" s="16"/>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F75" s="16"/>
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F76" s="16"/>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F77" s="16"/>
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" s="16"/>
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" s="16"/>
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80" s="16"/>
+      <c r="G80" s="12"/>
+    </row>
+    <row r="81" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" s="16"/>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F82" s="16"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F84" s="16"/>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F85" s="16"/>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F86" s="16"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F87" s="16"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F88" s="16"/>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F89" s="16"/>
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F90" s="16"/>
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F91" s="16"/>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" s="16"/>
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F93" s="16"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="16"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" s="16"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96" s="16"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F97" s="16"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F98" s="16"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F99" s="16"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F100" s="16"/>
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F101" s="16"/>
+      <c r="G101" s="12"/>
+    </row>
+    <row r="102" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F102" s="16"/>
+      <c r="G102" s="12"/>
+    </row>
+    <row r="103" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" s="16"/>
+      <c r="G103" s="12"/>
+    </row>
+    <row r="104" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F104" s="16"/>
+      <c r="G104" s="12"/>
+    </row>
+    <row r="105" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F105" s="16"/>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F106" s="16"/>
+      <c r="G106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="16"/>
+      <c r="G107" s="12"/>
+    </row>
+    <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F108" s="16"/>
+      <c r="G108" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Template Import/Templates commission Draft.xlsx
+++ b/Template Import/Templates commission Draft.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CF7D77-901B-4AE8-ADB7-80ACBAE4D7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BBD4FD-15B8-4B05-8CC1-1475A2DAE349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
   </bookViews>
   <sheets>
     <sheet name="h" sheetId="1" r:id="rId1"/>
@@ -1669,23 +1669,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72421B36-76D0-40A6-BFD5-6431BAAA1FA9}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="6"/>
+    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1796,22 +1796,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617443EE-1F70-4C65-9F9D-8265A5A09A24}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="6"/>
+    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1914,12 +1914,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56115C20-D91B-46DD-B77B-B0C3859B037D}">
   <dimension ref="A1:G108"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="30.9140625" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="3" max="3" width="30.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="B1" s="16" t="s">
         <v>270</v>
       </c>
@@ -1929,7 +1930,7 @@
       </c>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -1946,7 +1947,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A3" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A4" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -1980,7 +1981,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A5" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A6" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2014,7 +2015,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A7" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2031,7 +2032,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A8" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A9" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A10" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2082,7 +2083,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A11" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2099,7 +2100,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A12" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2116,7 +2117,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A13" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A14" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2146,7 +2147,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A15" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2159,7 +2160,7 @@
       <c r="F15" s="16"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A16" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2172,7 +2173,7 @@
       <c r="F16" s="16"/>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A17" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2185,7 +2186,7 @@
       <c r="F17" s="16"/>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A18" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2198,7 +2199,7 @@
       <c r="F18" s="16"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A19" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2211,7 +2212,7 @@
       <c r="F19" s="16"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A20" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2224,7 +2225,7 @@
       <c r="F20" s="16"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A21" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2237,7 +2238,7 @@
       <c r="F21" s="16"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A22" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2250,7 +2251,7 @@
       <c r="F22" s="16"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A23" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2263,7 +2264,7 @@
       <c r="F23" s="16"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A24" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2276,7 +2277,7 @@
       <c r="F24" s="16"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A25" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2289,7 +2290,7 @@
       <c r="F25" s="16"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A26" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2302,7 +2303,7 @@
       <c r="F26" s="16"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A27" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2315,7 +2316,7 @@
       <c r="F27" s="16"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A28" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2328,7 +2329,7 @@
       <c r="F28" s="16"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A29" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2341,7 +2342,7 @@
       <c r="F29" s="16"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A30" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2354,7 +2355,7 @@
       <c r="F30" s="16"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A31" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2367,7 +2368,7 @@
       <c r="F31" s="16"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A32" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2380,7 +2381,7 @@
       <c r="F32" s="16"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A33" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2393,7 +2394,7 @@
       <c r="F33" s="16"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A34" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2406,7 +2407,7 @@
       <c r="F34" s="16"/>
       <c r="G34" s="12"/>
     </row>
-    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A35" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2419,7 +2420,7 @@
       <c r="F35" s="16"/>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A36" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2432,7 +2433,7 @@
       <c r="F36" s="16"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A37" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2445,7 +2446,7 @@
       <c r="F37" s="16"/>
       <c r="G37" s="12"/>
     </row>
-    <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A38" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2458,7 +2459,7 @@
       <c r="F38" s="16"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A39" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2471,7 +2472,7 @@
       <c r="F39" s="16"/>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A40" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2484,7 +2485,7 @@
       <c r="F40" s="16"/>
       <c r="G40" s="12"/>
     </row>
-    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A41" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2497,7 +2498,7 @@
       <c r="F41" s="16"/>
       <c r="G41" s="12"/>
     </row>
-    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A42" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2510,7 +2511,7 @@
       <c r="F42" s="16"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A43" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2523,7 +2524,7 @@
       <c r="F43" s="16"/>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A44" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2536,7 +2537,7 @@
       <c r="F44" s="16"/>
       <c r="G44" s="12"/>
     </row>
-    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A45" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2549,7 +2550,7 @@
       <c r="F45" s="16"/>
       <c r="G45" s="12"/>
     </row>
-    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A46" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2562,7 +2563,7 @@
       <c r="F46" s="16"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A47" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2575,7 +2576,7 @@
       <c r="F47" s="16"/>
       <c r="G47" s="12"/>
     </row>
-    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A48" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2588,7 +2589,7 @@
       <c r="F48" s="16"/>
       <c r="G48" s="12"/>
     </row>
-    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A49" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2601,7 +2602,7 @@
       <c r="F49" s="16"/>
       <c r="G49" s="12"/>
     </row>
-    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A50" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2614,7 +2615,7 @@
       <c r="F50" s="16"/>
       <c r="G50" s="12"/>
     </row>
-    <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A51" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2627,7 +2628,7 @@
       <c r="F51" s="16"/>
       <c r="G51" s="12"/>
     </row>
-    <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A52" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2640,7 +2641,7 @@
       <c r="F52" s="16"/>
       <c r="G52" s="12"/>
     </row>
-    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A53" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2653,7 +2654,7 @@
       <c r="F53" s="16"/>
       <c r="G53" s="12"/>
     </row>
-    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A54" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2666,7 +2667,7 @@
       <c r="F54" s="16"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A55" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2679,7 +2680,7 @@
       <c r="F55" s="16"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A56" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2692,7 +2693,7 @@
       <c r="F56" s="16"/>
       <c r="G56" s="12"/>
     </row>
-    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A57" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2705,7 +2706,7 @@
       <c r="F57" s="16"/>
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A58" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2718,7 +2719,7 @@
       <c r="F58" s="16"/>
       <c r="G58" s="12"/>
     </row>
-    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A59" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2731,7 +2732,7 @@
       <c r="F59" s="16"/>
       <c r="G59" s="12"/>
     </row>
-    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A60" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2744,7 +2745,7 @@
       <c r="F60" s="16"/>
       <c r="G60" s="12"/>
     </row>
-    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A61" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2757,7 +2758,7 @@
       <c r="F61" s="16"/>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A62" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2770,7 +2771,7 @@
       <c r="F62" s="16"/>
       <c r="G62" s="12"/>
     </row>
-    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A63" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2783,7 +2784,7 @@
       <c r="F63" s="16"/>
       <c r="G63" s="12"/>
     </row>
-    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A64" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2796,7 +2797,7 @@
       <c r="F64" s="16"/>
       <c r="G64" s="12"/>
     </row>
-    <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A65" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2809,7 +2810,7 @@
       <c r="F65" s="16"/>
       <c r="G65" s="12"/>
     </row>
-    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A66" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2822,7 +2823,7 @@
       <c r="F66" s="16"/>
       <c r="G66" s="12"/>
     </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A67" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2835,7 +2836,7 @@
       <c r="F67" s="16"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A68" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2848,7 +2849,7 @@
       <c r="F68" s="16"/>
       <c r="G68" s="12"/>
     </row>
-    <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A69" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2861,7 +2862,7 @@
       <c r="F69" s="16"/>
       <c r="G69" s="12"/>
     </row>
-    <row r="70" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A70" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2874,7 +2875,7 @@
       <c r="F70" s="16"/>
       <c r="G70" s="12"/>
     </row>
-    <row r="71" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A71" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2887,7 +2888,7 @@
       <c r="F71" s="16"/>
       <c r="G71" s="12"/>
     </row>
-    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A72" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2900,7 +2901,7 @@
       <c r="F72" s="16"/>
       <c r="G72" s="12"/>
     </row>
-    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A73" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2913,7 +2914,7 @@
       <c r="F73" s="16"/>
       <c r="G73" s="12"/>
     </row>
-    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A74" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2926,7 +2927,7 @@
       <c r="F74" s="16"/>
       <c r="G74" s="12"/>
     </row>
-    <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A75" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2939,7 +2940,7 @@
       <c r="F75" s="16"/>
       <c r="G75" s="12"/>
     </row>
-    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A76" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2952,7 +2953,7 @@
       <c r="F76" s="16"/>
       <c r="G76" s="12"/>
     </row>
-    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A77" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2965,7 +2966,7 @@
       <c r="F77" s="16"/>
       <c r="G77" s="12"/>
     </row>
-    <row r="78" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A78" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2978,7 +2979,7 @@
       <c r="F78" s="16"/>
       <c r="G78" s="12"/>
     </row>
-    <row r="79" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A79" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -2991,7 +2992,7 @@
       <c r="F79" s="16"/>
       <c r="G79" s="12"/>
     </row>
-    <row r="80" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A80" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3004,7 +3005,7 @@
       <c r="F80" s="16"/>
       <c r="G80" s="12"/>
     </row>
-    <row r="81" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A81" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3017,7 +3018,7 @@
       <c r="F81" s="16"/>
       <c r="G81" s="12"/>
     </row>
-    <row r="82" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A82" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3030,7 +3031,7 @@
       <c r="F82" s="16"/>
       <c r="G82" s="12"/>
     </row>
-    <row r="83" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A83" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3043,7 +3044,7 @@
       <c r="F83" s="16"/>
       <c r="G83" s="12"/>
     </row>
-    <row r="84" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A84" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3056,7 +3057,7 @@
       <c r="F84" s="16"/>
       <c r="G84" s="12"/>
     </row>
-    <row r="85" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A85" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3069,7 +3070,7 @@
       <c r="F85" s="16"/>
       <c r="G85" s="12"/>
     </row>
-    <row r="86" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A86" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3082,7 +3083,7 @@
       <c r="F86" s="16"/>
       <c r="G86" s="12"/>
     </row>
-    <row r="87" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A87" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3095,7 +3096,7 @@
       <c r="F87" s="16"/>
       <c r="G87" s="12"/>
     </row>
-    <row r="88" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A88" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3108,7 +3109,7 @@
       <c r="F88" s="16"/>
       <c r="G88" s="12"/>
     </row>
-    <row r="89" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A89" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3121,7 +3122,7 @@
       <c r="F89" s="16"/>
       <c r="G89" s="12"/>
     </row>
-    <row r="90" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A90" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3134,7 +3135,7 @@
       <c r="F90" s="16"/>
       <c r="G90" s="12"/>
     </row>
-    <row r="91" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A91" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3147,7 +3148,7 @@
       <c r="F91" s="16"/>
       <c r="G91" s="12"/>
     </row>
-    <row r="92" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A92" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3160,7 +3161,7 @@
       <c r="F92" s="16"/>
       <c r="G92" s="12"/>
     </row>
-    <row r="93" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A93" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3173,7 +3174,7 @@
       <c r="F93" s="16"/>
       <c r="G93" s="12"/>
     </row>
-    <row r="94" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A94" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3186,7 +3187,7 @@
       <c r="F94" s="16"/>
       <c r="G94" s="12"/>
     </row>
-    <row r="95" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A95" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3199,7 +3200,7 @@
       <c r="F95" s="16"/>
       <c r="G95" s="12"/>
     </row>
-    <row r="96" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A96" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3212,7 +3213,7 @@
       <c r="F96" s="16"/>
       <c r="G96" s="12"/>
     </row>
-    <row r="97" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A97" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3225,7 +3226,7 @@
       <c r="F97" s="16"/>
       <c r="G97" s="12"/>
     </row>
-    <row r="98" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A98" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3238,7 +3239,7 @@
       <c r="F98" s="16"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A99" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3251,7 +3252,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="12"/>
     </row>
-    <row r="100" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A100" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3264,7 +3265,7 @@
       <c r="F100" s="16"/>
       <c r="G100" s="12"/>
     </row>
-    <row r="101" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A101" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3277,7 +3278,7 @@
       <c r="F101" s="16"/>
       <c r="G101" s="12"/>
     </row>
-    <row r="102" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A102" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3290,7 +3291,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A103" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3303,7 +3304,7 @@
       <c r="F103" s="16"/>
       <c r="G103" s="12"/>
     </row>
-    <row r="104" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A104" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3316,7 +3317,7 @@
       <c r="F104" s="16"/>
       <c r="G104" s="12"/>
     </row>
-    <row r="105" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A105" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3329,7 +3330,7 @@
       <c r="F105" s="16"/>
       <c r="G105" s="12"/>
     </row>
-    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A106" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3342,7 +3343,7 @@
       <c r="F106" s="16"/>
       <c r="G106" s="12"/>
     </row>
-    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A107" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -3355,7 +3356,7 @@
       <c r="F107" s="16"/>
       <c r="G107" s="12"/>
     </row>
-    <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A108" s="16">
         <v>4033.0010000000002</v>
       </c>

--- a/Template Import/Templates commission Draft.xlsx
+++ b/Template Import/Templates commission Draft.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BBD4FD-15B8-4B05-8CC1-1475A2DAE349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED68BB7-A165-4B56-8BAD-E420E46777EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
   </bookViews>
   <sheets>
     <sheet name="h" sheetId="1" r:id="rId1"/>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="284">
   <si>
     <t>DocNum</t>
   </si>
@@ -456,9 +456,6 @@
     <t>01</t>
   </si>
   <si>
-    <t>IG00</t>
-  </si>
-  <si>
     <t>LAK</t>
   </si>
   <si>
@@ -1183,6 +1180,48 @@
   </si>
   <si>
     <t>VENDOR</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>COM-Credit Life</t>
+  </si>
+  <si>
+    <t>COM-Engineering</t>
+  </si>
+  <si>
+    <t>COM-FIRE</t>
+  </si>
+  <si>
+    <t>COM-Health</t>
+  </si>
+  <si>
+    <t>COM-IAR</t>
+  </si>
+  <si>
+    <t>COM-Marine</t>
+  </si>
+  <si>
+    <t>COM-MISC</t>
+  </si>
+  <si>
+    <t>COM-Motor Compulsory</t>
+  </si>
+  <si>
+    <t>COM-Motor Voluntary</t>
+  </si>
+  <si>
+    <t>COM-PA</t>
+  </si>
+  <si>
+    <t>COM-Property</t>
+  </si>
+  <si>
+    <t>ນາງ ວຽງສະໄໝ ແສງຈຳພອນ</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -1711,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1746,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>8</v>
@@ -1763,10 +1802,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>12</v>
@@ -1880,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -1892,17 +1931,17 @@
         <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="G3" s="6">
         <v>1000000</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1913,24 +1952,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56115C20-D91B-46DD-B77B-B0C3859B037D}">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.09765625" customWidth="1"/>
     <col min="3" max="3" width="30.8984375" customWidth="1"/>
+    <col min="4" max="4" width="24.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="B1" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="F1" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="2" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="E1" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="16">
         <v>4033.0010000000002</v>
       </c>
@@ -1938,1436 +1981,1472 @@
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="F2" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="D2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F2" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A3" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="F3" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="D3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F3" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A4" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="D4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F4" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A5" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="D5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F5" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A6" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="F6" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="D6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F6" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A7" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="F7" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="D7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F7" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A8" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="F8" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F8" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A9" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F9" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="D9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F9" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A10" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="D10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F10" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A11" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F11" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A12" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="C12" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F12" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A13" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F13" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="D13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="F13" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A14" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>220</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A15" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A16" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A17" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B17" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A16" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A17" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>217</v>
-      </c>
       <c r="C17" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>215</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A18" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>213</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A19" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A20" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A20" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="C20" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>210</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A21" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>208</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A22" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>206</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A23" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>204</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A24" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>202</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A25" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>200</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A26" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>198</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A27" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>196</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A28" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>194</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A29" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>192</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A30" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>190</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A31" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>188</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A32" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>186</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A33" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>184</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A34" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>182</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A35" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>180</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A36" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>178</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A37" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>176</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A38" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>174</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A39" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>172</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A40" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>170</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A41" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="12"/>
-    </row>
-    <row r="42" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>168</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A42" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="12"/>
-    </row>
-    <row r="43" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>166</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A43" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="12"/>
-    </row>
-    <row r="44" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>164</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A44" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="12"/>
-    </row>
-    <row r="45" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>162</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A45" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="12"/>
-    </row>
-    <row r="46" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>160</v>
+      </c>
+      <c r="E45" s="16"/>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A46" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="12"/>
-    </row>
-    <row r="47" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>158</v>
+      </c>
+      <c r="E46" s="16"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A47" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="12"/>
-    </row>
-    <row r="48" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>156</v>
+      </c>
+      <c r="E47" s="16"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A48" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="12"/>
-    </row>
-    <row r="49" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>154</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A49" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="12"/>
-    </row>
-    <row r="50" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>152</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A50" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="12"/>
-    </row>
-    <row r="51" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>150</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A51" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="12"/>
-    </row>
-    <row r="52" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>148</v>
+      </c>
+      <c r="E51" s="16"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A52" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="12"/>
-    </row>
-    <row r="53" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>146</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A53" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="12"/>
-    </row>
-    <row r="54" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A54" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="12"/>
-    </row>
-    <row r="55" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>142</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A55" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="12"/>
-    </row>
-    <row r="56" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>140</v>
+      </c>
+      <c r="E55" s="16"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A56" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="12"/>
-    </row>
-    <row r="57" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>138</v>
+      </c>
+      <c r="E56" s="16"/>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A57" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="12"/>
-    </row>
-    <row r="58" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>136</v>
+      </c>
+      <c r="E57" s="16"/>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A58" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="12"/>
-    </row>
-    <row r="59" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>134</v>
+      </c>
+      <c r="E58" s="16"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A59" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="12"/>
-    </row>
-    <row r="60" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>132</v>
+      </c>
+      <c r="E59" s="16"/>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A60" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="12"/>
-    </row>
-    <row r="61" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>130</v>
+      </c>
+      <c r="E60" s="16"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A61" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="12"/>
-    </row>
-    <row r="62" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>128</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A62" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="12"/>
-    </row>
-    <row r="63" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>126</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A63" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="12"/>
-    </row>
-    <row r="64" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>124</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A64" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="12"/>
-    </row>
-    <row r="65" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>122</v>
+      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A65" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="12"/>
-    </row>
-    <row r="66" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>120</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A66" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="12"/>
-    </row>
-    <row r="67" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>118</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A67" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="12"/>
-    </row>
-    <row r="68" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>116</v>
+      </c>
+      <c r="E67" s="16"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A68" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F68" s="16"/>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>114</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A69" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="12"/>
-    </row>
-    <row r="70" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>112</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A70" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="12"/>
-    </row>
-    <row r="71" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>110</v>
+      </c>
+      <c r="E70" s="16"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A71" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="12"/>
-    </row>
-    <row r="72" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>108</v>
+      </c>
+      <c r="E71" s="16"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A72" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="12"/>
-    </row>
-    <row r="73" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>106</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A73" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="12"/>
-    </row>
-    <row r="74" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>104</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A74" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F74" s="16"/>
-      <c r="G74" s="12"/>
-    </row>
-    <row r="75" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>102</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A75" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="12"/>
-    </row>
-    <row r="76" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>100</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A76" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="F76" s="16"/>
-      <c r="G76" s="12"/>
-    </row>
-    <row r="77" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>98</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A77" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="12"/>
-    </row>
-    <row r="78" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>96</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A78" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="12"/>
-    </row>
-    <row r="79" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>94</v>
+      </c>
+      <c r="E78" s="16"/>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A79" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="12"/>
-    </row>
-    <row r="80" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>92</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A80" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="12"/>
-    </row>
-    <row r="81" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>90</v>
+      </c>
+      <c r="E80" s="16"/>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A81" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="12"/>
-    </row>
-    <row r="82" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>88</v>
+      </c>
+      <c r="E81" s="16"/>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A82" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="12"/>
-    </row>
-    <row r="83" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>86</v>
+      </c>
+      <c r="E82" s="16"/>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A83" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F83" s="16"/>
-      <c r="G83" s="12"/>
-    </row>
-    <row r="84" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>84</v>
+      </c>
+      <c r="E83" s="16"/>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A84" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="12"/>
-    </row>
-    <row r="85" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>82</v>
+      </c>
+      <c r="E84" s="16"/>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A85" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="12"/>
-    </row>
-    <row r="86" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>80</v>
+      </c>
+      <c r="E85" s="16"/>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A86" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="12"/>
-    </row>
-    <row r="87" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>78</v>
+      </c>
+      <c r="E86" s="16"/>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A87" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="12"/>
-    </row>
-    <row r="88" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>76</v>
+      </c>
+      <c r="E87" s="16"/>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A88" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="12"/>
-    </row>
-    <row r="89" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>74</v>
+      </c>
+      <c r="E88" s="16"/>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A89" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F89" s="16"/>
-      <c r="G89" s="12"/>
-    </row>
-    <row r="90" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>72</v>
+      </c>
+      <c r="E89" s="16"/>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A90" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="12"/>
-    </row>
-    <row r="91" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>70</v>
+      </c>
+      <c r="E90" s="16"/>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A91" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F91" s="16"/>
-      <c r="G91" s="12"/>
-    </row>
-    <row r="92" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>68</v>
+      </c>
+      <c r="E91" s="16"/>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A92" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F92" s="16"/>
-      <c r="G92" s="12"/>
-    </row>
-    <row r="93" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>66</v>
+      </c>
+      <c r="E92" s="16"/>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A93" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F93" s="16"/>
-      <c r="G93" s="12"/>
-    </row>
-    <row r="94" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>64</v>
+      </c>
+      <c r="E93" s="16"/>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A94" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F94" s="16"/>
-      <c r="G94" s="12"/>
-    </row>
-    <row r="95" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>62</v>
+      </c>
+      <c r="E94" s="16"/>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A95" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F95" s="16"/>
-      <c r="G95" s="12"/>
-    </row>
-    <row r="96" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>60</v>
+      </c>
+      <c r="E95" s="16"/>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A96" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F96" s="16"/>
-      <c r="G96" s="12"/>
-    </row>
-    <row r="97" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>58</v>
+      </c>
+      <c r="E96" s="16"/>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A97" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F97" s="16"/>
-      <c r="G97" s="12"/>
-    </row>
-    <row r="98" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>56</v>
+      </c>
+      <c r="E97" s="16"/>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A98" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F98" s="16"/>
-      <c r="G98" s="12"/>
-    </row>
-    <row r="99" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>54</v>
+      </c>
+      <c r="E98" s="16"/>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A99" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F99" s="16"/>
-      <c r="G99" s="12"/>
-    </row>
-    <row r="100" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>52</v>
+      </c>
+      <c r="E99" s="16"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A100" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F100" s="16"/>
-      <c r="G100" s="12"/>
-    </row>
-    <row r="101" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>50</v>
+      </c>
+      <c r="E100" s="16"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A101" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F101" s="16"/>
-      <c r="G101" s="12"/>
-    </row>
-    <row r="102" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>48</v>
+      </c>
+      <c r="E101" s="16"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A102" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F102" s="16"/>
-      <c r="G102" s="12"/>
-    </row>
-    <row r="103" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>46</v>
+      </c>
+      <c r="E102" s="16"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A103" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F103" s="16"/>
-      <c r="G103" s="12"/>
-    </row>
-    <row r="104" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>44</v>
+      </c>
+      <c r="E103" s="16"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A104" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F104" s="16"/>
-      <c r="G104" s="12"/>
-    </row>
-    <row r="105" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>42</v>
+      </c>
+      <c r="E104" s="16"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A105" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F105" s="16"/>
-      <c r="G105" s="12"/>
-    </row>
-    <row r="106" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>40</v>
+      </c>
+      <c r="E105" s="16"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A106" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F106" s="16"/>
-      <c r="G106" s="12"/>
-    </row>
-    <row r="107" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>38</v>
+      </c>
+      <c r="E106" s="16"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A107" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F107" s="16"/>
-      <c r="G107" s="12"/>
-    </row>
-    <row r="108" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.5">
+        <v>36</v>
+      </c>
+      <c r="E107" s="16"/>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
       <c r="A108" s="16">
         <v>4033.0010000000002</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F108" s="16"/>
-      <c r="G108" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="E108" s="16"/>
+      <c r="F108" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Template Import/Templates commission Draft.xlsx
+++ b/Template Import/Templates commission Draft.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B509430-ABBB-471E-8918-D87EA10AF28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED68BB7-A165-4B56-8BAD-E420E46777EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
   </bookViews>
   <sheets>
     <sheet name="h" sheetId="1" r:id="rId1"/>
     <sheet name="l" sheetId="2" r:id="rId2"/>
+    <sheet name="VENDOR+PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="284">
   <si>
     <t>DocNum</t>
   </si>
@@ -455,9 +456,6 @@
     <t>01</t>
   </si>
   <si>
-    <t>IG00</t>
-  </si>
-  <si>
     <t>LAK</t>
   </si>
   <si>
@@ -474,13 +472,763 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂຊກໄຊ ພລັສ ອີ-ຄອມເມີດ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-OAP-0002</t>
+  </si>
+  <si>
+    <t>ຂາຍຜ່ານແອັບອອນລາຍ</t>
+  </si>
+  <si>
+    <t>V-VT-OAP-0001</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນຈຸລະພາກທີ່ບໍ່ຮັບເງິນຝາກມັນນີ.ລາ ຈຳກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0004</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນ ອາລຸນໄຫມ່</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0002</t>
+  </si>
+  <si>
+    <t>ສະຖາບັນການເງິນ ໂຊກໄຊ</t>
+  </si>
+  <si>
+    <t>V-VT-LS-0001</t>
+  </si>
+  <si>
+    <t>ນຸ້ຍ ສີປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0046</t>
+  </si>
+  <si>
+    <t>ພາວະລິນ ສີສະຫວັດ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0016</t>
+  </si>
+  <si>
+    <t>ພົງພາວັນ ມໍໄລພອນ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0013</t>
+  </si>
+  <si>
+    <t>ຂາຍຕົງຜູ້ຂາຍຂາຍເອງ ແລະ ມີການແນະນຳ</t>
+  </si>
+  <si>
+    <t>V-VT-ITF-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ລາວໂຕໂຢຕ້າ ບໍລິການ ຈຳກັດ (ສາຂາ ສີໂຄດ)</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0009</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ລາວໂຕໂຢຕ້າ ບໍລິການ ຈຳກັດ (ສາຂາ ທົ່ງຂັນຄຳ)</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0007</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ເອັມພາຍ ມໍເຕີ ລາວ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0006</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂອໂຕ ລາວ ຈຳກັຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0003</t>
+  </si>
+  <si>
+    <t>ຮ້ານ ຄຳທະວີ ປະດັບຍົນ</t>
+  </si>
+  <si>
+    <t>V-VT-DL-0001</t>
+  </si>
+  <si>
+    <t>ລູກຄ້າເຂົ້າມາຊື້ຕົງ</t>
+  </si>
+  <si>
+    <t>V-VT-D-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ໃຈອາລີ ອິນທະວົງ (ທະນາຄານ ລາວ-ຝຣັ່ງ)</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0005</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ເອຊີລິດາ QH</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0004</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ສົ່ງເສີມ ກະສິກຳ HQ</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0002</t>
+  </si>
+  <si>
+    <t>Maruhun HQ</t>
+  </si>
+  <si>
+    <t>V-VT-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ພີເອັສຊີ ນາຍໜ້າປະກັນໄພ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0007</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ສາຍຝົນ ໂບຼກເກີ</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0004</t>
+  </si>
+  <si>
+    <t>KX BROKER</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0002</t>
+  </si>
+  <si>
+    <t>OAC BROKER</t>
+  </si>
+  <si>
+    <t>V-VT-BK-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ນ້ອຍ ສິລິມົງຄຸນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0075</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພູມິນ ໄກສອນເພັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0074</t>
+  </si>
+  <si>
+    <t>ນາງ ສຸດາພອນ ໂງ່ນກະເສີມສຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0072</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນມາລີ ຄັນທະວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0071</t>
+  </si>
+  <si>
+    <t>ນາງ ສິນໃຈ ໄຊຍະລາດ (ບໍລິສັດ ສຸກໃຈ ບໍລິການ ຈັດຫາງານ ຈໍາກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0069</t>
+  </si>
+  <si>
+    <t>ນາງ ວາດສະໜາ ວໍລະວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0068</t>
+  </si>
+  <si>
+    <t>ທ້າວ ເພັດສະພອນ ບຸນຍະນິດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0067</t>
+  </si>
+  <si>
+    <t>ນາງ ເພັດມະນີ ວໍລະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0065</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ຊີທີໄອ ໂລຈິດສະຕິກ (ລາວ) ຈຳກັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0063</t>
+  </si>
+  <si>
+    <t>ນາງ ເກດສະໜາ ແສງທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0060</t>
+  </si>
+  <si>
+    <t>ນາງ ພູລິນິດ ອິນສີຊຽງໃໝ່</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0059</t>
+  </si>
+  <si>
+    <t>ນາງ ຂັນຄຳ ພົມມະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0058</t>
+  </si>
+  <si>
+    <t>ນາງ ນ້ອຍນາລີ ກຽດຕາວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0057</t>
+  </si>
+  <si>
+    <t>ນາງ ວິດາພອນ ໄພສານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0056</t>
+  </si>
+  <si>
+    <t>ທ້າວ ທອງວັນ ຄຳວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0055</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພອນໄຊ ຈັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0054</t>
+  </si>
+  <si>
+    <t>ນາງ ຈຸລະພອນ ເພັງສະຫວັດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0053</t>
+  </si>
+  <si>
+    <t>ທ້າວ ວິພາກອນ ໂພທິສານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0051</t>
+  </si>
+  <si>
+    <t>ນາງ ພຸດທະສະຫວັນ ສັງໄຊຍະລາດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0050</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສົມອົກ ວິຣະສັກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0049</t>
+  </si>
+  <si>
+    <t>ນາງ ວິໄລລັກ ຄຳວົງສາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0048</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສອນປະເສີດ ພູມມາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0046</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ 14 ມີໄຊການຄ້າຂາອອກ-ຂາເຂົ້າ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0042</t>
+  </si>
+  <si>
+    <t>ນາງ ທອງໃສ ສິດຊະນະ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0040</t>
+  </si>
+  <si>
+    <t>ນາງ ນຸດດາວັນ ນວນສະຫວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0036</t>
+  </si>
+  <si>
+    <t>ທ້າວ ອິນທະຕອງ ແກ້ວສີລາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0035</t>
+  </si>
+  <si>
+    <t>ນາງ ລີຕ້າ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0034</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພານິດໄຊ ສີບຸນຍາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0028</t>
+  </si>
+  <si>
+    <t>ນາງ ສຸວັນທອນ ໄຊຍະລາດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0025</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນທະລົມ ລັດຖະມອນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0023</t>
+  </si>
+  <si>
+    <t>ນາງ ຈ່ອນນີ້ ກຸລາວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0021</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໂຊກໄຊຈະເລີນຂົນສົ່ງ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0020</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຈັນສະໝອນ ໄຊຍະກຸມມານ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0018</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳຈັນ ຊາມູນຕີຮ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0017</t>
+  </si>
+  <si>
+    <t>ນາງ ຈຳປາເພັດ ສຸທຳມະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0016</t>
+  </si>
+  <si>
+    <t>ທ້າວ ທອງພູນ ຂຸນບັນດິດ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0015</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳຜັນ ຈັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0014</t>
+  </si>
+  <si>
+    <t>ນາງ ອຳພາພອນ ແຕ້ອຳພອນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0012</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພູມະສອນ ຮ່ວງຫວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0011</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳສີ ສີລິມຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0010</t>
+  </si>
+  <si>
+    <t>ນາງ ບົວລະພັນ ພົມສຸວັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0009</t>
+  </si>
+  <si>
+    <t>ນາງ ອໍລະວີ ວິໄລວົງ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0006</t>
+  </si>
+  <si>
+    <t>ນາງ ອຸດທະວີວອນ ບຸນທະຄຳ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0005</t>
+  </si>
+  <si>
+    <t>ທ້າວ ກິດຕິສັກ ນັນທະນາ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0004</t>
+  </si>
+  <si>
+    <t>ທ້າວ ດວງພະຈັນ ສິງທອງມົນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003-06</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສີອຳພອນ ແສງສຸລິນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003-02</t>
+  </si>
+  <si>
+    <t>ນາງ ບຸນຮຽງ ຈັນທະສຸກ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0003</t>
+  </si>
+  <si>
+    <t>ນາງ ທິບພາພອນ ພົມມະຈັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0002</t>
+  </si>
+  <si>
+    <t>ທ້າວ ກຸ້ງ ສີນວນຈັນ</t>
+  </si>
+  <si>
+    <t>V-VT-AG-0001</t>
+  </si>
+  <si>
+    <t>ຄຳພູນ ສີດາວົງ</t>
+  </si>
+  <si>
+    <t>V-ST-ITF-0001</t>
+  </si>
+  <si>
+    <t>LAO TOYOTA SOUTHERN</t>
+  </si>
+  <si>
+    <t>V-ST-DL-0001</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ມາຣູຮານ ສາຂາ ຈຳປາສັກ</t>
+  </si>
+  <si>
+    <t>V-ST-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ນາຍໜ້າປະກັນໄພ ອາລາດິນ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-ST-BK-0001</t>
+  </si>
+  <si>
+    <t>ທ້າວ ເພັດສະໝອນ ສີລາເພັດ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0012</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄູນສະຫວັດ ວັນທອງ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0011</t>
+  </si>
+  <si>
+    <t>ນາງ ເກດມະນີ ຄູນວິໄຊ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0009</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສົມພິດ ພົມມະຈັກ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0008</t>
+  </si>
+  <si>
+    <t>ທ້າວ ບຸຸດສະດີ ສີພັນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0007</t>
+  </si>
+  <si>
+    <t>ນາງ ມະນີີວັນ ໄຊອາສາ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0005</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ເອັດສແອລ ທ່ອງທ່ຽວ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0004</t>
+  </si>
+  <si>
+    <t>ນາງ ສີອໍາພອນ ແກ້ວໂກມິນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0003</t>
+  </si>
+  <si>
+    <t>ນາງ ດາວພະໄທ ໄຊຍະສອນ</t>
+  </si>
+  <si>
+    <t>V-ST-AG-0001</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>V-PMT-0001</t>
+  </si>
+  <si>
+    <t>ທ້າວ ໄຊ ວື</t>
+  </si>
+  <si>
+    <t>V-NT-ITF-0001</t>
+  </si>
+  <si>
+    <t>ທະນາຄານ ມາຣູຮານ ສາຂາ ຫຼວງພະບາງ</t>
+  </si>
+  <si>
+    <t>V-NT-BNK-0001</t>
+  </si>
+  <si>
+    <t>ບໍລິສັດ ໄຊຍະສິດ ໂບຣກເກີ້ ຈຳກັດຜູ້ດຽວ</t>
+  </si>
+  <si>
+    <t>V-NT-BK-0001-02</t>
+  </si>
+  <si>
+    <t>V-NT-BK-0001</t>
+  </si>
+  <si>
+    <t>ນາງ ລາທິນ ສີສົມສັກ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0015</t>
+  </si>
+  <si>
+    <t>ນາງ ແກ້ວອາມິດ ມີໄຊຄຳ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0013</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສີທະນົນ ພົມແສງປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0011</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0006</t>
+  </si>
+  <si>
+    <t>ທ້າວ ດອນແກ້ວ ວົງນາທີ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0002</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອື່ນໆ</t>
+  </si>
+  <si>
+    <t>624.13.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ອຳພອນ ພັນທະວົງ</t>
+  </si>
+  <si>
+    <t>V-NT-AG-0001</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>624.12.00</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0020</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>624.11.00</t>
+  </si>
+  <si>
+    <t>ນາງ ພອນມະນີ ຂຸນທຳ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0016</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຄວາມສ່ຽງອຸດສາຫະກຳ</t>
+  </si>
+  <si>
+    <t>624.10.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສຸລິຍາ ພົມຂັນໄຊ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0014</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>624.09.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄິດສະໜາ ອຸ່ນແກ້ວມະນິວົງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0011</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>624.08.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈິນຕະນາ ນໍລະສິງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0010</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ສູຂະພາບ</t>
+  </si>
+  <si>
+    <t>624.07.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ບຸນທະນອງ ຄຸນພະຈັນ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0007</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອຸບັດຕິເຫດສ່ວນບູກຄົນ</t>
+  </si>
+  <si>
+    <t>624.06.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນນະພາ ພອນມະນີ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0006</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>624.05.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄາລາເຕ້ ເທບພະວົງ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0005</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>624.04.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ວົງສຸລິວັນ ວັນນະໄລ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0004</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກສະຫມັກໃຈ</t>
+  </si>
+  <si>
+    <t>624.03.00</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຄຳແສງ ໄຊປະເສີດ</t>
+  </si>
+  <si>
+    <t>V-MS-AG-0002</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍຜົນຕອບແທນ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>624.02.00</t>
+  </si>
+  <si>
+    <t>ນາງ ຈັນສຸດາ ຈັນທະດວງສີ</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>COM-Credit Life</t>
+  </si>
+  <si>
+    <t>COM-Engineering</t>
+  </si>
+  <si>
+    <t>COM-FIRE</t>
+  </si>
+  <si>
+    <t>COM-Health</t>
+  </si>
+  <si>
+    <t>COM-IAR</t>
+  </si>
+  <si>
+    <t>COM-Marine</t>
+  </si>
+  <si>
+    <t>COM-MISC</t>
+  </si>
+  <si>
+    <t>COM-Motor Compulsory</t>
+  </si>
+  <si>
+    <t>COM-Motor Voluntary</t>
+  </si>
+  <si>
+    <t>COM-PA</t>
+  </si>
+  <si>
+    <t>COM-Property</t>
+  </si>
+  <si>
+    <t>ນາງ ວຽງສະໄໝ ແສງຈຳພອນ</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,6 +1281,12 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -597,7 +1351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -618,6 +1372,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,7 +1708,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72421B36-76D0-40A6-BFD5-6431BAAA1FA9}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
@@ -969,7 +1724,7 @@
     <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -995,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1004,7 +1759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>8</v>
@@ -1039,7 +1794,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1047,10 +1802,10 @@
         <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>12</v>
@@ -1080,7 +1835,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617443EE-1F70-4C65-9F9D-8265A5A09A24}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
@@ -1095,7 +1850,7 @@
     <col min="11" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1159,12 +1914,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -1176,21 +1931,1524 @@
         <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="G3" s="6">
         <v>1000000</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56115C20-D91B-46DD-B77B-B0C3859B037D}">
+  <dimension ref="A1:F108"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="3" max="3" width="30.8984375" customWidth="1"/>
+    <col min="4" max="4" width="24.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="B1" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A2" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A3" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A4" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A5" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A6" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A7" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A8" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A9" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A10" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A11" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A12" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A13" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A14" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A15" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A16" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A17" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A18" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A19" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A20" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A21" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A22" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A23" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A24" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A25" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A26" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A27" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A28" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A29" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A30" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A31" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A32" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A33" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A34" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A35" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A36" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A37" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" s="16"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A38" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="16"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A39" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A40" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="16"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A41" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A42" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A43" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E43" s="16"/>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A44" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A45" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="16"/>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A46" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="16"/>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A47" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="16"/>
+      <c r="F47" s="12"/>
+    </row>
+    <row r="48" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A48" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="12"/>
+    </row>
+    <row r="49" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A49" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="12"/>
+    </row>
+    <row r="50" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A50" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A51" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51" s="16"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A52" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A53" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A54" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" s="16"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A55" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E55" s="16"/>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A56" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E56" s="16"/>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A57" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" s="16"/>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A58" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="16"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A59" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E59" s="16"/>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A60" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="16"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A61" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A62" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A63" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A64" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="12"/>
+    </row>
+    <row r="65" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A65" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="12"/>
+    </row>
+    <row r="66" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A66" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="12"/>
+    </row>
+    <row r="67" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A67" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E67" s="16"/>
+      <c r="F67" s="12"/>
+    </row>
+    <row r="68" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A68" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="12"/>
+    </row>
+    <row r="69" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A69" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="12"/>
+    </row>
+    <row r="70" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A70" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" s="16"/>
+      <c r="F70" s="12"/>
+    </row>
+    <row r="71" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A71" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E71" s="16"/>
+      <c r="F71" s="12"/>
+    </row>
+    <row r="72" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A72" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A73" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A74" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A75" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A76" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A77" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A78" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="16"/>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A79" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A80" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" s="16"/>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A81" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E81" s="16"/>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A82" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E82" s="16"/>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A83" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" s="16"/>
+      <c r="F83" s="12"/>
+    </row>
+    <row r="84" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A84" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" s="16"/>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A85" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E85" s="16"/>
+      <c r="F85" s="12"/>
+    </row>
+    <row r="86" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A86" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E86" s="16"/>
+      <c r="F86" s="12"/>
+    </row>
+    <row r="87" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A87" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E87" s="16"/>
+      <c r="F87" s="12"/>
+    </row>
+    <row r="88" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A88" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="16"/>
+      <c r="F88" s="12"/>
+    </row>
+    <row r="89" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A89" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E89" s="16"/>
+      <c r="F89" s="12"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A90" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E90" s="16"/>
+      <c r="F90" s="12"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A91" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="16"/>
+      <c r="F91" s="12"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A92" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" s="16"/>
+      <c r="F92" s="12"/>
+    </row>
+    <row r="93" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A93" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E93" s="16"/>
+      <c r="F93" s="12"/>
+    </row>
+    <row r="94" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A94" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" s="16"/>
+      <c r="F94" s="12"/>
+    </row>
+    <row r="95" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A95" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E95" s="16"/>
+      <c r="F95" s="12"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A96" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E96" s="16"/>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A97" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E97" s="16"/>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A98" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E98" s="16"/>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A99" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E99" s="16"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A100" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E100" s="16"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A101" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E101" s="16"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="102" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A102" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E102" s="16"/>
+      <c r="F102" s="12"/>
+    </row>
+    <row r="103" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A103" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E103" s="16"/>
+      <c r="F103" s="12"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A104" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E104" s="16"/>
+      <c r="F104" s="12"/>
+    </row>
+    <row r="105" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A105" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E105" s="16"/>
+      <c r="F105" s="12"/>
+    </row>
+    <row r="106" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A106" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106" s="16"/>
+      <c r="F106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A107" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" s="16"/>
+      <c r="F107" s="12"/>
+    </row>
+    <row r="108" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A108" s="16">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E108" s="16"/>
+      <c r="F108" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Template Import/Templates commission Draft.xlsx
+++ b/Template Import/Templates commission Draft.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED68BB7-A165-4B56-8BAD-E420E46777EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCEA1F1-C49F-4709-AAAB-9DEC7C81D901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D786836-D1CC-4A96-BEEA-65DBFDF6ABE2}"/>
   </bookViews>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="322">
   <si>
     <t>DocNum</t>
   </si>
@@ -411,9 +411,6 @@
     <t>V-MS-AG-0001</t>
   </si>
   <si>
-    <t>Annie</t>
-  </si>
-  <si>
     <t>Commission</t>
   </si>
   <si>
@@ -462,9 +459,6 @@
     <t>Agent</t>
   </si>
   <si>
-    <t>20260623</t>
-  </si>
-  <si>
     <t>COM-TA</t>
   </si>
   <si>
@@ -1222,13 +1216,136 @@
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t>MS-FE-26-00396</t>
+  </si>
+  <si>
+    <t>MS-MGPA-26-362GG</t>
+  </si>
+  <si>
+    <t>MS-MGPH-26-377JB</t>
+  </si>
+  <si>
+    <t>MS-M-26-473139</t>
+  </si>
+  <si>
+    <t>MS-M-26-149381</t>
+  </si>
+  <si>
+    <t>MS-M-26-642385</t>
+  </si>
+  <si>
+    <t>MS-M-26-032783</t>
+  </si>
+  <si>
+    <t>MS-M-26-009704</t>
+  </si>
+  <si>
+    <t>MS-M-26-905007</t>
+  </si>
+  <si>
+    <t>MS-M-26-795592</t>
+  </si>
+  <si>
+    <t>MS-M-26-490871</t>
+  </si>
+  <si>
+    <t>MS-M-26-604578</t>
+  </si>
+  <si>
+    <t>MS-M-26-194752</t>
+  </si>
+  <si>
+    <t>MS-M-26-923323</t>
+  </si>
+  <si>
+    <t>MS-M-26-262465</t>
+  </si>
+  <si>
+    <t>MS-M-26-717903</t>
+  </si>
+  <si>
+    <t>MS-M-26-008004</t>
+  </si>
+  <si>
+    <t>MS-M-26-262950</t>
+  </si>
+  <si>
+    <t>Mr. Kong Wanjun</t>
+  </si>
+  <si>
+    <t>AKX TRADING CO.,LTD</t>
+  </si>
+  <si>
+    <t>Laemthong trading Sole Co., LTD</t>
+  </si>
+  <si>
+    <t>ນາງ ອຸດົມຄອນ  ວິສີສົມບັດ</t>
+  </si>
+  <si>
+    <t>ທ້າວ ອາທິສັກ ຣັຕະນະວົງ</t>
+  </si>
+  <si>
+    <t>ນາງ ຫອມມາລາ ສຸວັນນະວົງ</t>
+  </si>
+  <si>
+    <t>ທ້າວ ສາຍພອນ ອາມາດມົນຕີ</t>
+  </si>
+  <si>
+    <t>ທ້າວ ຫັດສະດີ ສຸລິຍະໄທ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ທ້າວ ສົມພະໄທ  ຈັນທະລັງສີ </t>
+  </si>
+  <si>
+    <t>ນາງ ທອງບາງ ແມນວິໄລ</t>
+  </si>
+  <si>
+    <t>ທ້າວ ພູແກ້ວ ໄຊຍະພູມີ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ອົງການຊ່ວຍເຫຼືອເດັກສາກົນ (Save the children) ປະຈຳ ສປປ ລາວ   </t>
+  </si>
+  <si>
+    <t>VT-ITF-0009</t>
+  </si>
+  <si>
+    <t>VT-BK-0002</t>
+  </si>
+  <si>
+    <t>VT-AG-0004</t>
+  </si>
+  <si>
+    <t>VT-AG-0001</t>
+  </si>
+  <si>
+    <t>VT-DL-0009</t>
+  </si>
+  <si>
+    <t>VT-DL-0007</t>
+  </si>
+  <si>
+    <t>ST-BNK-0001</t>
+  </si>
+  <si>
+    <t>ST-DL-0001</t>
+  </si>
+  <si>
+    <t>VT-BK-0001</t>
+  </si>
+  <si>
+    <t>Broker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1288,6 +1405,37 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1339,7 +1487,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1347,11 +1495,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1365,19 +1546,52 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma 14" xfId="1" xr:uid="{EAA46545-B916-458F-930B-8F87E7A93596}"/>
+    <cellStyle name="Comma 17" xfId="2" xr:uid="{9F805538-2880-44D2-BB71-C0D03A789A94}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1707,19 +1921,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72421B36-76D0-40A6-BFD5-6431BAAA1FA9}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="50.09765625" style="6" customWidth="1"/>
     <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
     <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
@@ -1731,7 +1945,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -1750,7 +1964,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>8</v>
@@ -1766,7 +1980,7 @@
       <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="20" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1785,7 +1999,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>8</v>
@@ -1801,14 +2015,14 @@
       <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>12</v>
+      <c r="C3" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D3" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>312</v>
       </c>
       <c r="G3" s="6">
         <v>111</v>
@@ -1816,17 +2030,516 @@
       <c r="H3" s="6">
         <v>18</v>
       </c>
-      <c r="I3" s="6">
-        <v>56</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D4" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="G4" s="6">
+        <v>111</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D5" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" s="6">
+        <v>111</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D6" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G6" s="6">
+        <v>111</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D7" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" s="6">
+        <v>111</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D8" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="G8" s="6">
+        <v>111</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D9" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="G9" s="6">
+        <v>111</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D10" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="G10" s="6">
+        <v>111</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D11" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="6">
+        <v>111</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D12" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="6">
+        <v>111</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D13" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="G13" s="6">
+        <v>111</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D14" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G14" s="6">
+        <v>111</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D15" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G15" s="6">
+        <v>111</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6">
         <v>14</v>
       </c>
+      <c r="B16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D16" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G16" s="6">
+        <v>111</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D17" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G17" s="6">
+        <v>111</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D18" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G18" s="6">
+        <v>111</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D19" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G19" s="6">
+        <v>111</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="D20" s="21">
+        <v>20260624</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="G20" s="6">
+        <v>111</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I3:I20">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>ISNUMBER(MATCH(I3,$DN:$DN,0))</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -1834,13 +2547,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617443EE-1F70-4C65-9F9D-8265A5A09A24}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="21.19921875" style="6" customWidth="1"/>
     <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" style="14" customWidth="1"/>
     <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
@@ -1851,35 +2564,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1887,64 +2600,558 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>31</v>
+      <c r="B3" t="s">
+        <v>276</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="22">
+        <v>302186</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="22">
+        <v>302186</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="G3" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="22">
+        <v>72727</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" s="22">
+        <v>72727</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="22">
+        <v>20976000</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" s="22">
+        <v>20976000</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="6" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22">
+        <v>167960</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="22">
+        <v>167960</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
       </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="22">
+        <v>101554</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G7" s="22">
+        <v>101554</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1009009</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G8" s="22">
+        <v>1009009</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>1590811</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" s="22">
+        <v>1590811</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22">
+        <v>928288</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" s="22">
+        <v>928288</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="22">
+        <v>92980</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="22">
+        <v>92980</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="22">
+        <v>1446306</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="22">
+        <v>1446306</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>928288</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G13" s="22">
+        <v>928288</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G14" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G15" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G19" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="22">
+        <v>83220</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G20" s="22">
+        <v>83220</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>321</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -1961,1492 +3168,1492 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A2" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A3" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A4" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A5" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A6" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A7" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A8" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A9" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A10" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A11" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A12" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A2" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A3" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A5" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A6" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A7" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A8" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A9" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D9" t="s">
-        <v>281</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A10" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E12" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A13" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" t="s">
         <v>275</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A11" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" t="s">
-        <v>272</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A12" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D12" t="s">
-        <v>271</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A13" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>222</v>
+      <c r="E13" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A14" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A15" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="A15" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
+      <c r="A16" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A16" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A17" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="12"/>
+      <c r="A17" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="15"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A18" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="12"/>
+      <c r="A18" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A19" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="A19" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="12"/>
+      <c r="C19" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A20" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A21" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="12"/>
+      <c r="A21" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A22" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="12"/>
+      <c r="A22" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A23" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="12"/>
+      <c r="A23" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A24" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="12"/>
+      <c r="A24" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A25" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="12"/>
+      <c r="A25" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A26" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="12"/>
+      <c r="A26" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A27" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="12"/>
+      <c r="A27" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A28" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A29" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="12"/>
+      <c r="A29" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A30" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="12"/>
+      <c r="A30" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A31" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A32" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="12"/>
+      <c r="A32" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="15"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A33" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="12"/>
+      <c r="A33" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A34" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="12"/>
+      <c r="A34" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A35" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="12"/>
+      <c r="A35" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A36" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="12"/>
+      <c r="A36" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A37" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="12"/>
+      <c r="A37" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A38" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="12"/>
+      <c r="A38" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A39" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="12"/>
+      <c r="A39" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A40" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="12"/>
+      <c r="A40" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A41" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="12"/>
+      <c r="A41" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="11"/>
     </row>
     <row r="42" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A42" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="12"/>
+      <c r="A42" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A43" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="12"/>
+      <c r="A43" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A44" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" s="16"/>
-      <c r="F44" s="12"/>
+      <c r="A44" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A45" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="12"/>
+      <c r="A45" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="11"/>
     </row>
     <row r="46" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A46" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E46" s="16"/>
-      <c r="F46" s="12"/>
+      <c r="A46" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A47" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" s="16"/>
-      <c r="F47" s="12"/>
+      <c r="A47" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A48" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="12"/>
+      <c r="A48" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A49" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="12"/>
+      <c r="A49" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A50" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="16"/>
-      <c r="F50" s="12"/>
+      <c r="A50" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A51" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E51" s="16"/>
-      <c r="F51" s="12"/>
+      <c r="A51" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A52" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="E52" s="16"/>
-      <c r="F52" s="12"/>
+      <c r="A52" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A53" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E53" s="16"/>
-      <c r="F53" s="12"/>
+      <c r="A53" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="15"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A54" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" s="16"/>
-      <c r="F54" s="12"/>
+      <c r="A54" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A55" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E55" s="16"/>
-      <c r="F55" s="12"/>
+      <c r="A55" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A56" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E56" s="16"/>
-      <c r="F56" s="12"/>
+      <c r="A56" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A57" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="12"/>
+      <c r="A57" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A58" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="12"/>
+      <c r="A58" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A59" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="12"/>
+      <c r="A59" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="15"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A60" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="12"/>
+      <c r="A60" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A61" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="12"/>
+      <c r="A61" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A62" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="12"/>
+      <c r="A62" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A63" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="12"/>
+      <c r="A63" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E63" s="15"/>
+      <c r="F63" s="11"/>
     </row>
     <row r="64" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A64" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="12"/>
+      <c r="A64" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E64" s="15"/>
+      <c r="F64" s="11"/>
     </row>
     <row r="65" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A65" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="12"/>
+      <c r="A65" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E65" s="15"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A66" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="12"/>
+      <c r="A66" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" s="15"/>
+      <c r="F66" s="11"/>
     </row>
     <row r="67" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A67" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="12"/>
+      <c r="A67" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="15"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A68" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="12"/>
+      <c r="A68" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" s="15"/>
+      <c r="F68" s="11"/>
     </row>
     <row r="69" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A69" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="12"/>
+      <c r="A69" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E69" s="15"/>
+      <c r="F69" s="11"/>
     </row>
     <row r="70" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A70" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="12"/>
+      <c r="A70" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A71" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="12"/>
+      <c r="A71" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E71" s="15"/>
+      <c r="F71" s="11"/>
     </row>
     <row r="72" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A72" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="12"/>
+      <c r="A72" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72" s="15"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A73" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="12"/>
+      <c r="A73" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="15"/>
+      <c r="F73" s="11"/>
     </row>
     <row r="74" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A74" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B74" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="12"/>
+      <c r="A74" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="15"/>
+      <c r="F74" s="11"/>
     </row>
     <row r="75" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A75" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="12"/>
+      <c r="A75" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="11"/>
     </row>
     <row r="76" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A76" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B76" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="12"/>
+      <c r="A76" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="11"/>
     </row>
     <row r="77" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A77" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B77" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" s="16"/>
-      <c r="F77" s="12"/>
+      <c r="A77" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E77" s="15"/>
+      <c r="F77" s="11"/>
     </row>
     <row r="78" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A78" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E78" s="16"/>
-      <c r="F78" s="12"/>
+      <c r="A78" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="15"/>
+      <c r="F78" s="11"/>
     </row>
     <row r="79" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A79" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="12"/>
+      <c r="A79" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79" s="15"/>
+      <c r="F79" s="11"/>
     </row>
     <row r="80" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A80" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="12"/>
+      <c r="A80" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="15"/>
+      <c r="F80" s="11"/>
     </row>
     <row r="81" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A81" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E81" s="16"/>
-      <c r="F81" s="12"/>
+      <c r="A81" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E81" s="15"/>
+      <c r="F81" s="11"/>
     </row>
     <row r="82" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A82" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E82" s="16"/>
-      <c r="F82" s="12"/>
+      <c r="A82" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="15"/>
+      <c r="F82" s="11"/>
     </row>
     <row r="83" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A83" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B83" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="12"/>
+      <c r="A83" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" s="15"/>
+      <c r="F83" s="11"/>
     </row>
     <row r="84" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A84" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B84" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="12"/>
+      <c r="A84" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E84" s="15"/>
+      <c r="F84" s="11"/>
     </row>
     <row r="85" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A85" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="12"/>
+      <c r="A85" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E85" s="15"/>
+      <c r="F85" s="11"/>
     </row>
     <row r="86" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A86" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E86" s="16"/>
-      <c r="F86" s="12"/>
+      <c r="A86" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E86" s="15"/>
+      <c r="F86" s="11"/>
     </row>
     <row r="87" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A87" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="12"/>
+      <c r="A87" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E87" s="15"/>
+      <c r="F87" s="11"/>
     </row>
     <row r="88" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A88" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B88" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="12"/>
+      <c r="A88" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E88" s="15"/>
+      <c r="F88" s="11"/>
     </row>
     <row r="89" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A89" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B89" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="12"/>
+      <c r="A89" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="15"/>
+      <c r="F89" s="11"/>
     </row>
     <row r="90" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A90" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E90" s="16"/>
-      <c r="F90" s="12"/>
+      <c r="A90" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" s="15"/>
+      <c r="F90" s="11"/>
     </row>
     <row r="91" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A91" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E91" s="16"/>
-      <c r="F91" s="12"/>
+      <c r="A91" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E91" s="15"/>
+      <c r="F91" s="11"/>
     </row>
     <row r="92" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A92" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="12"/>
+      <c r="A92" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="15"/>
+      <c r="F92" s="11"/>
     </row>
     <row r="93" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A93" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B93" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="12"/>
+      <c r="A93" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E93" s="15"/>
+      <c r="F93" s="11"/>
     </row>
     <row r="94" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A94" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B94" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="12"/>
+      <c r="A94" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E94" s="15"/>
+      <c r="F94" s="11"/>
     </row>
     <row r="95" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A95" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B95" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="12"/>
+      <c r="A95" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E95" s="15"/>
+      <c r="F95" s="11"/>
     </row>
     <row r="96" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A96" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B96" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="12"/>
+      <c r="A96" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E96" s="15"/>
+      <c r="F96" s="11"/>
     </row>
     <row r="97" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A97" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="12"/>
+      <c r="A97" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E97" s="15"/>
+      <c r="F97" s="11"/>
     </row>
     <row r="98" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A98" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="12"/>
+      <c r="A98" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" s="15"/>
+      <c r="F98" s="11"/>
     </row>
     <row r="99" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A99" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B99" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="12"/>
+      <c r="A99" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E99" s="15"/>
+      <c r="F99" s="11"/>
     </row>
     <row r="100" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A100" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E100" s="16"/>
-      <c r="F100" s="12"/>
+      <c r="A100" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E100" s="15"/>
+      <c r="F100" s="11"/>
     </row>
     <row r="101" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A101" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E101" s="16"/>
-      <c r="F101" s="12"/>
+      <c r="A101" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101" s="15"/>
+      <c r="F101" s="11"/>
     </row>
     <row r="102" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A102" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B102" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E102" s="16"/>
-      <c r="F102" s="12"/>
+      <c r="A102" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E102" s="15"/>
+      <c r="F102" s="11"/>
     </row>
     <row r="103" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A103" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B103" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="12"/>
+      <c r="A103" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E103" s="15"/>
+      <c r="F103" s="11"/>
     </row>
     <row r="104" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A104" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B104" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E104" s="16"/>
-      <c r="F104" s="12"/>
+      <c r="A104" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E104" s="15"/>
+      <c r="F104" s="11"/>
     </row>
     <row r="105" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A105" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E105" s="16"/>
-      <c r="F105" s="12"/>
+      <c r="A105" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" s="15"/>
+      <c r="F105" s="11"/>
     </row>
     <row r="106" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A106" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B106" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E106" s="16"/>
-      <c r="F106" s="12"/>
+      <c r="A106" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" s="15"/>
+      <c r="F106" s="11"/>
     </row>
     <row r="107" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A107" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B107" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E107" s="16"/>
-      <c r="F107" s="12"/>
+      <c r="A107" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E107" s="15"/>
+      <c r="F107" s="11"/>
     </row>
     <row r="108" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.5">
-      <c r="A108" s="16">
-        <v>4033.0010000000002</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C108" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E108" s="16"/>
-      <c r="F108" s="12"/>
+      <c r="A108" s="15">
+        <v>4033.0010000000002</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E108" s="15"/>
+      <c r="F108" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
